--- a/Mod_Korean/Lang/KR/Game/Game.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Game.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6132" uniqueCount="3976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6133" uniqueCount="3976">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">weather_Rain</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">It begins to rain.</t>
@@ -8460,7 +8460,7 @@
     <t xml:space="preserve">#1 inject(s) #2 with #3.</t>
   </si>
   <si>
-    <t xml:space="preserve">#1は#3で#2に注射した。</t>
+    <t xml:space="preserve">#1は#3を#2に刺した。</t>
   </si>
   <si>
     <t xml:space="preserve">isIn</t>
@@ -29551,7 +29551,7 @@
         <v>2766</v>
       </c>
       <c r="B938" t="s">
-        <v>2922</v>
+        <v>7</v>
       </c>
       <c r="C938"/>
       <c r="D938" t="s">
